--- a/data/★2026년 제안 심사 취합본(AI).xlsx
+++ b/data/★2026년 제안 심사 취합본(AI).xlsx
@@ -1,24 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\★백업\16.제안제도\2026년\7. 제안관리 AI포함\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DD28CE-55D2-4FE2-AB48-609F4836D1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$135</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="362">
   <si>
     <t>연 번</t>
   </si>
@@ -288,31 +282,9 @@
     <t>계정등록 신청서 양식 간소화로 업무 간소화</t>
   </si>
   <si>
-    <t>이동우</t>
-  </si>
-  <si>
     <t>공원수련관관리처 수련관운영부</t>
   </si>
   <si>
-    <t xml:space="preserve">체육 5급 </t>
-  </si>
-  <si>
-    <t>[지정제안] 안전취약 지역 비상벨 설치를 통한 안전사고 예방 및 신속 대응체계 구축</t>
-  </si>
-  <si>
-    <t>중복</t>
-  </si>
-  <si>
-    <t>중복 가능성 높음(채택)</t>
-  </si>
-  <si>
-    <t>2025-06-080 화장실 및 탈의실 내 비상벨 설치를 통한 안전사고 예방 시스템 구축
-심사결과: 채택 [2025년 제안 총괄 !I71]</t>
-  </si>
-  <si>
-    <t>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 화장실·탈의실에 비상벨을 설치하고 종합상황실과 연동하여 위급상황을 즉시 전달하는 제안임. 이번도 안전취약지역 중 탈의실 우선 설치가 핵심으로 대상·수단·효과가 겹침. 전수조사·위치번호·훈련 추가만으로 차별성이 충분한지 검토 필요.</t>
-  </si>
-  <si>
     <t>윤지혜</t>
   </si>
   <si>
@@ -401,19 +373,6 @@
   </si>
   <si>
     <t>[지정제안] AI 신규회원 스마트 적응 시뮬레이션 구축</t>
-  </si>
-  <si>
-    <t>박왕권</t>
-  </si>
-  <si>
-    <t>선제적 제습관리를 통한 시민회관 결로 예방 및 시설환경 개선</t>
-  </si>
-  <si>
-    <t>2025-07-101 시민회관 지하층 결로 방지 위한 제습기 설치
-심사결과: 채택 [2025년 제안 총괄 !I91]</t>
-  </si>
-  <si>
-    <t>2025-07-101의 심사결과가 채택임. 시민회관 동일 주요 출입구 5개소의 산업용 제습기 설치·24시간 운전·공조 병행·빙상장 관람창 결로 방지가 일치함. 단가·효과검증·중앙계단 추가는 보완 요소임. 2023-06-012는 채택결과 미확인으로 판단 근거에서 제외함.</t>
   </si>
   <si>
     <t>윤귀환</t>
@@ -594,16 +553,6 @@
     <t>행정 4급</t>
   </si>
   <si>
-    <t>(자유제안) 화장실 위생 개선 및 노로바이러스 감염 예방을 위한 양변기 손잡이 설치</t>
-  </si>
-  <si>
-    <t>2021-04-020 개인위생 강화를 위한 화장실 변기뚜껑 손잡이 설치(코로나19 확산방지)
-심사결과: 채택 [2022년 제안!G20]</t>
-  </si>
-  <si>
-    <t>2021-04-020은 심사결과 채택으로 확인됨. 변기 뚜껑에 손잡이를 부착하여 직접 접촉을 줄이고 위생을 개선하는 핵심 수단·목적이 이번 제안과 같음. 2024-07-117은 부적합이므로 중복 판단 근거에서 제외함. 항균 소재·안내 스티커 추가의 차별성은 별도 검토 필요.</t>
-  </si>
-  <si>
     <t>곽용후</t>
   </si>
   <si>
@@ -804,22 +753,6 @@
     <t>시설이용 고객을 위한 안전수칙 제작 및 게시</t>
   </si>
   <si>
-    <t>선우효</t>
-  </si>
-  <si>
-    <t>[지정제안] 링크장 바닥 유도 안내 표시 설치</t>
-  </si>
-  <si>
-    <t>2025-04-014 빙상장 입구 유도선 부착</t>
-  </si>
-  <si>
-    <t>2025-04-014 빙상장 입구 유도선 부착
-심사결과: 채택 [2025년 제안 총괄 !I13]</t>
-  </si>
-  <si>
-    <t>기존 표시의 비교안 2025-04-014는 채택으로 확인됨. 대여실·링크장 출입구에 색상 바닥 유도선을 설치해 동선을 안내하는 목적·수단이 겹침. 실제 제안서의 안내구간·색상·시공 범위가 같은지 최종 확인 필요.</t>
-  </si>
-  <si>
     <t>오준영</t>
   </si>
   <si>
@@ -883,23 +816,7 @@
     <t>[지정제안] 일시고용 근로시간 통합관리용 파일 구축</t>
   </si>
   <si>
-    <t>김성진</t>
-  </si>
-  <si>
     <t>수련관운영부</t>
-  </si>
-  <si>
-    <t>[지정제안] 청소년수련관 주차장 트렌치 덮개 설치를 통한 안전사고 예방</t>
-  </si>
-  <si>
-    <t>2025-10-134 청소년 수련관 주차장 트렌치 개선</t>
-  </si>
-  <si>
-    <t>2025-10-134 청소년 수련관 주차장 트렌치 개선
-심사결과: 채택 [2025년 제안 총괄 !I123]</t>
-  </si>
-  <si>
-    <t>2025-10-134는 총괄 시트와 일반제안(채택) 시트에서 채택으로 확인됨. 같은 청소년수련관 주차장의 노출 트렌치에 안전형 덮개를 설치하여 발 빠짐을 예방하는 내용으로 핵심 대상·조치가 일치함. 소재·격자와 설치구간 차이는 확인 필요.</t>
   </si>
   <si>
     <t>박태준</t>
@@ -1097,42 +1014,9 @@
     <t>[지정제안] 설계용역 과업변경에 따른 계약금액 조정기준 마련</t>
   </si>
   <si>
-    <t>김상철</t>
-  </si>
-  <si>
-    <t>시스템에어컨 실외기 차양막(커버) 설치</t>
-  </si>
-  <si>
-    <t>공영주차장 정산소 에어컨 실외기 커버 설치
-심사결과: 채택 [2021년 제안!I55, 연번 52]</t>
-  </si>
-  <si>
-    <t>공영주차장 정산소 에어컨 실외기 커버 제안은 2021년 제안 시트 55행에서 채택으로 확인됨. 실외기 상부 햇빛 차단으로 냉방효율·전기료를 개선하는 수단과 효과가 같음. 정산소에서 별관·체육관동 옥상으로 장소가 바뀌고 통풍·반사재 선택을 보완한 점은 별도 검토 필요.</t>
-  </si>
-  <si>
     <t>[지정제안] 공사근로자 노무비 청구 및 지급관리 기준 마련</t>
   </si>
   <si>
-    <t>[지정제안] AI 체육시설 홈페이지 맞춤형 챗봇 도입</t>
-  </si>
-  <si>
-    <t>2026-121 카카오톡 챗봇 연계형 보이는 ARS 서비스 구축</t>
-  </si>
-  <si>
-    <t>중복접수(2026)</t>
-  </si>
-  <si>
-    <t>2026 게시판 121 카카오톡 챗봇 연계형 보이는 ARS 서비스 구축
-채택결과 미확인 [Sheet1!M113:N113]
-2024-07-096 디지털 플랫폼 정부구현을 위한 스마트 공공기관 챗봇 도입
-심사결과: 불채택 [2024년 제안!I201]
-2025-06-065 도시공사 민원업무 효율화를 위한 AI 자동응답 시스템 도입
-심사결과: 과락3명 [2025년 제안 총괄 !I56]</t>
-  </si>
-  <si>
-    <t>기존 중복(2026) 표시를 재검토함. 게시판 121번은 평점·과락구분이 비어 있어 채택을 확인할 수 없음. 별도 과거 챗봇 비교안도 각각 불채택·과락3명임. 제목·자동응대 기능만으로 채택된 제안과 중복이라고 할 수 없어 기존 중복 표시는 보류로 수정함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</t>
-  </si>
-  <si>
     <t>박소원</t>
   </si>
   <si>
@@ -1179,22 +1063,6 @@
   </si>
   <si>
     <t>시니어 안전지킴이</t>
-  </si>
-  <si>
-    <t>조홍원</t>
-  </si>
-  <si>
-    <t>QR코드를 활용한 "운동 전 자가 안전 확인제" 도입</t>
-  </si>
-  <si>
-    <t>2026-75 운동 전 10초! 자가안전확인제 운영</t>
-  </si>
-  <si>
-    <t>2026 게시판 75 운동 전 10초! 자가안전확인제 운영
-채택결과 미확인 [Sheet1!M67:N67]</t>
-  </si>
-  <si>
-    <t>기존 중복(2026) 표시를 재검토함. 자가확인 증상·QR 안내·운동 자제 방식은 유사하지만 게시판 75번의 평점·과락구분이 비어 있어 채택을 확인할 수 없음. 현재 접수 제안끼리의 유사성과 채택안 중복은 구분해야 하므로 보류로 수정함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</t>
   </si>
   <si>
     <t>최성훈</t>
@@ -1275,19 +1143,11 @@
   <si>
     <t>완강기 빨간 테이프 부착을 통한 소방시설 시인성 개선 제안</t>
   </si>
-  <si>
-    <t xml:space="preserve">중복 </t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>중복</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
@@ -1371,7 +1231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1412,11 +1272,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF1FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1476,7 +1331,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1615,45 +1470,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal" xfId="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1977,9 +1796,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:R143"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R135"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.375" style="1" customWidth="1"/>
@@ -2719,54 +2537,46 @@
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
     </row>
-    <row r="18" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A18" s="46">
-        <f t="shared" ref="A18:A49" si="1">ROW()-1</f>
+    <row r="18" spans="1:18" ht="63.95" customHeight="1">
+      <c r="A18" s="36">
+        <f t="shared" ref="A18:A47" si="1">ROW()-1</f>
         <v>17</v>
       </c>
-      <c r="B18" s="47">
-        <v>23</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="48" t="s">
+      <c r="B18" s="37">
+        <v>24</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="D18" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="49">
-        <v>46237.302777777775</v>
-      </c>
-      <c r="J18" s="50" t="s">
+      <c r="E18" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="46" t="s">
+      <c r="F18" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="39">
+        <v>46238.454166666663</v>
+      </c>
+      <c r="J18" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="L18" s="50"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q18" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="55" t="s">
-        <v>89</v>
-      </c>
+      <c r="K18" s="36"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
     </row>
     <row r="19" spans="1:18" ht="63.95" customHeight="1">
       <c r="A19" s="36">
@@ -2774,31 +2584,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>50</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="I19" s="39">
-        <v>46238.454166666663</v>
+        <v>46238.459722222222</v>
       </c>
       <c r="J19" s="40" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K19" s="36"/>
       <c r="L19" s="40"/>
@@ -2809,37 +2619,37 @@
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
     </row>
-    <row r="20" spans="1:18" ht="63.95" customHeight="1">
+    <row r="20" spans="1:18" ht="19.5" customHeight="1">
       <c r="A20" s="36">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B20" s="37">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="I20" s="39">
-        <v>46238.459722222222</v>
+        <v>46238.48055555555</v>
       </c>
       <c r="J20" s="40" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K20" s="36"/>
       <c r="L20" s="40"/>
@@ -2856,13 +2666,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="37">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E21" s="38" t="s">
         <v>30</v>
@@ -2871,16 +2681,16 @@
         <v>20</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="I21" s="39">
-        <v>46238.48055555555</v>
+        <v>46238.527083333334</v>
       </c>
       <c r="J21" s="40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K21" s="36"/>
       <c r="L21" s="40"/>
@@ -2897,31 +2707,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="37">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F22" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="I22" s="39">
-        <v>46238.527083333334</v>
+        <v>46239.888888888891</v>
       </c>
       <c r="J22" s="40" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K22" s="36"/>
       <c r="L22" s="40"/>
@@ -2938,31 +2748,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="37">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F23" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I23" s="39">
-        <v>46239.888888888891</v>
+        <v>46240.429166666669</v>
       </c>
       <c r="J23" s="40" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K23" s="36"/>
       <c r="L23" s="40"/>
@@ -2979,31 +2789,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="37">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F24" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I24" s="39">
-        <v>46240.429166666669</v>
+        <v>46240.740972222222</v>
       </c>
       <c r="J24" s="40" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K24" s="36"/>
       <c r="L24" s="40"/>
@@ -3020,31 +2830,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="37">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="F25" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H25" s="38" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="I25" s="39">
-        <v>46240.740972222222</v>
+        <v>46241.381944444445</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K25" s="36"/>
       <c r="L25" s="40"/>
@@ -3061,31 +2871,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="37">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="F26" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H26" s="38" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I26" s="39">
-        <v>46241.381944444445</v>
+        <v>46241.764583333337</v>
       </c>
       <c r="J26" s="40" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K26" s="36"/>
       <c r="L26" s="40"/>
@@ -3102,31 +2912,31 @@
         <v>26</v>
       </c>
       <c r="B27" s="37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F27" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="I27" s="39">
-        <v>46241.764583333337</v>
+        <v>46244.345833333333</v>
       </c>
       <c r="J27" s="40" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K27" s="36"/>
       <c r="L27" s="40"/>
@@ -3143,31 +2953,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28" s="39">
+        <v>46244.586111111115</v>
+      </c>
+      <c r="J28" s="40" t="s">
         <v>112</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="I28" s="39">
-        <v>46244.345833333333</v>
-      </c>
-      <c r="J28" s="40" t="s">
-        <v>114</v>
       </c>
       <c r="K28" s="36"/>
       <c r="L28" s="40"/>
@@ -3184,31 +2994,31 @@
         <v>28</v>
       </c>
       <c r="B29" s="37">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F29" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="I29" s="39">
-        <v>46244.586111111115</v>
+        <v>46244.824999999997</v>
       </c>
       <c r="J29" s="40" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K29" s="36"/>
       <c r="L29" s="40"/>
@@ -3219,54 +3029,46 @@
       <c r="Q29" s="12"/>
       <c r="R29" s="12"/>
     </row>
-    <row r="30" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A30" s="46">
+    <row r="30" spans="1:18" ht="19.5" customHeight="1">
+      <c r="A30" s="36">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B30" s="47">
-        <v>36</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="49">
-        <v>46244.636111111111</v>
-      </c>
-      <c r="J30" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="K30" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="L30" s="50"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="53"/>
-      <c r="P30" s="54" t="s">
+      <c r="B30" s="37">
+        <v>38</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="Q30" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="R30" s="55" t="s">
-        <v>123</v>
-      </c>
+      <c r="E30" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="I30" s="39">
+        <v>46246.657638888893</v>
+      </c>
+      <c r="J30" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="K30" s="36"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
     </row>
     <row r="31" spans="1:18" ht="19.5" customHeight="1">
       <c r="A31" s="36">
@@ -3274,31 +3076,31 @@
         <v>30</v>
       </c>
       <c r="B31" s="37">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F31" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="I31" s="39">
-        <v>46244.824999999997</v>
+        <v>46246.743055555555</v>
       </c>
       <c r="J31" s="40" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K31" s="36"/>
       <c r="L31" s="40"/>
@@ -3315,31 +3117,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="37">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F32" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="I32" s="39">
-        <v>46246.657638888893</v>
+        <v>46247.488888888889</v>
       </c>
       <c r="J32" s="40" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K32" s="36"/>
       <c r="L32" s="40"/>
@@ -3350,37 +3152,37 @@
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
     </row>
-    <row r="33" spans="1:18" ht="19.5" customHeight="1">
+    <row r="33" spans="1:18" ht="63.95" customHeight="1">
       <c r="A33" s="36">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B33" s="37">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="I33" s="39">
-        <v>46246.743055555555</v>
+        <v>46247.40625</v>
       </c>
       <c r="J33" s="40" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K33" s="36"/>
       <c r="L33" s="40"/>
@@ -3397,31 +3199,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="37">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="I34" s="39">
-        <v>46247.488888888889</v>
+        <v>46247.408333333333</v>
       </c>
       <c r="J34" s="40" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K34" s="36"/>
       <c r="L34" s="40"/>
@@ -3432,46 +3234,52 @@
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
     </row>
-    <row r="35" spans="1:18" ht="63.95" customHeight="1">
+    <row r="35" spans="1:18" ht="87.95" customHeight="1">
       <c r="A35" s="36">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B35" s="37">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F35" s="36" t="s">
         <v>31</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="H35" s="38" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="I35" s="39">
-        <v>46247.40625</v>
+        <v>46247.410416666666</v>
       </c>
       <c r="J35" s="40" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K35" s="36"/>
       <c r="L35" s="40"/>
       <c r="M35" s="41"/>
       <c r="N35" s="25"/>
       <c r="O35" s="34"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
+      <c r="P35" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q35" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="R35" s="18" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="36" spans="1:18" ht="19.5" customHeight="1">
       <c r="A36" s="36">
@@ -3479,31 +3287,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G36" s="36" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="H36" s="38" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="I36" s="39">
-        <v>46247.408333333333</v>
+        <v>46247.477777777778</v>
       </c>
       <c r="J36" s="40" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K36" s="36"/>
       <c r="L36" s="40"/>
@@ -3514,52 +3322,46 @@
       <c r="Q36" s="12"/>
       <c r="R36" s="12"/>
     </row>
-    <row r="37" spans="1:18" ht="87.95" customHeight="1">
+    <row r="37" spans="1:18" ht="19.5" customHeight="1">
       <c r="A37" s="36">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B37" s="37">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="H37" s="38" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="I37" s="39">
-        <v>46247.410416666666</v>
+        <v>46247.481249999997</v>
       </c>
       <c r="J37" s="40" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K37" s="36"/>
       <c r="L37" s="40"/>
       <c r="M37" s="41"/>
       <c r="N37" s="25"/>
       <c r="O37" s="34"/>
-      <c r="P37" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q37" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="R37" s="18" t="s">
-        <v>140</v>
-      </c>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="12"/>
+      <c r="R37" s="12"/>
     </row>
     <row r="38" spans="1:18" ht="19.5" customHeight="1">
       <c r="A38" s="36">
@@ -3567,31 +3369,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="37">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="F38" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="H38" s="38" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I38" s="39">
-        <v>46247.477777777778</v>
+        <v>46247.681944444441</v>
       </c>
       <c r="J38" s="40" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="K38" s="36"/>
       <c r="L38" s="40"/>
@@ -3608,31 +3410,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="37">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F39" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I39" s="39">
-        <v>46247.481249999997</v>
+        <v>46283.667361111111</v>
       </c>
       <c r="J39" s="40" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K39" s="36"/>
       <c r="L39" s="40"/>
@@ -3649,31 +3451,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="37">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="F40" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="H40" s="38" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I40" s="39">
-        <v>46247.681944444441</v>
+        <v>46248.632638888885</v>
       </c>
       <c r="J40" s="40" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="40"/>
@@ -3690,31 +3492,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="37">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="F41" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="I41" s="39">
-        <v>46283.667361111111</v>
+        <v>46248.886111111111</v>
       </c>
       <c r="J41" s="40" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K41" s="36"/>
       <c r="L41" s="40"/>
@@ -3731,31 +3533,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="37">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F42" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="36" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="I42" s="39">
-        <v>46248.632638888885</v>
+        <v>46252.486805555556</v>
       </c>
       <c r="J42" s="40" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K42" s="36"/>
       <c r="L42" s="40"/>
@@ -3772,31 +3574,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="37">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D43" s="38" t="s">
         <v>39</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F43" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G43" s="36" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="I43" s="39">
-        <v>46248.886111111111</v>
+        <v>46252.547222222223</v>
       </c>
       <c r="J43" s="40" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="K43" s="36"/>
       <c r="L43" s="40"/>
@@ -3807,37 +3609,37 @@
       <c r="Q43" s="12"/>
       <c r="R43" s="12"/>
     </row>
-    <row r="44" spans="1:18" ht="19.5" customHeight="1">
+    <row r="44" spans="1:18" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="A44" s="36">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B44" s="37">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F44" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="36" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="I44" s="39">
-        <v>46252.486805555556</v>
+        <v>46253.372916666667</v>
       </c>
       <c r="J44" s="40" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="K44" s="36"/>
       <c r="L44" s="40"/>
@@ -3854,13 +3656,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="37">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E45" s="38" t="s">
         <v>19</v>
@@ -3869,16 +3671,16 @@
         <v>20</v>
       </c>
       <c r="G45" s="36" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="I45" s="39">
-        <v>46252.547222222223</v>
+        <v>46253.438194444447</v>
       </c>
       <c r="J45" s="40" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K45" s="36"/>
       <c r="L45" s="40"/>
@@ -3889,37 +3691,37 @@
       <c r="Q45" s="12"/>
       <c r="R45" s="12"/>
     </row>
-    <row r="46" spans="1:18" s="2" customFormat="1" ht="19.5" customHeight="1">
+    <row r="46" spans="1:18" ht="19.5" customHeight="1">
       <c r="A46" s="36">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B46" s="37">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F46" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I46" s="39">
-        <v>46253.372916666667</v>
+        <v>46253.734027777777</v>
       </c>
       <c r="J46" s="40" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="K46" s="36"/>
       <c r="L46" s="40"/>
@@ -3930,60 +3732,66 @@
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
     </row>
-    <row r="47" spans="1:18" ht="19.5" customHeight="1">
+    <row r="47" spans="1:18" ht="111.95" customHeight="1">
       <c r="A47" s="36">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B47" s="37">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="F47" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G47" s="36" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="H47" s="38" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="I47" s="39">
-        <v>46253.438194444447</v>
+        <v>46254.563888888893</v>
       </c>
       <c r="J47" s="40" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K47" s="36"/>
       <c r="L47" s="40"/>
       <c r="M47" s="41"/>
       <c r="N47" s="25"/>
       <c r="O47" s="34"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="12"/>
-      <c r="R47" s="12"/>
+      <c r="P47" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q47" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="R47" s="17" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="48" spans="1:18" ht="19.5" customHeight="1">
       <c r="A48" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A48:A77" si="2">ROW()-1</f>
         <v>47</v>
       </c>
       <c r="B48" s="37">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="E48" s="38" t="s">
         <v>80</v>
@@ -3992,16 +3800,16 @@
         <v>20</v>
       </c>
       <c r="G48" s="36" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I48" s="39">
-        <v>46253.734027777777</v>
+        <v>46255.490277777775</v>
       </c>
       <c r="J48" s="40" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="K48" s="36"/>
       <c r="L48" s="40"/>
@@ -4012,93 +3820,87 @@
       <c r="Q48" s="12"/>
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="1:18" ht="111.95" customHeight="1">
+    <row r="49" spans="1:18" ht="19.5" customHeight="1">
       <c r="A49" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="B49" s="37">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F49" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="H49" s="38" t="s">
         <v>54</v>
       </c>
       <c r="I49" s="39">
-        <v>46254.563888888893</v>
+        <v>46255.582638888889</v>
       </c>
       <c r="J49" s="40" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K49" s="36"/>
       <c r="L49" s="40"/>
       <c r="M49" s="41"/>
       <c r="N49" s="25"/>
       <c r="O49" s="34"/>
-      <c r="P49" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q49" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="R49" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="19.5" customHeight="1">
+      <c r="P49" s="27"/>
+      <c r="Q49" s="12"/>
+      <c r="R49" s="12"/>
+    </row>
+    <row r="50" spans="1:18" ht="87.95" customHeight="1">
       <c r="A50" s="36">
-        <f t="shared" ref="A50:A81" si="2">ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="B50" s="37">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="F50" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G50" s="36" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="I50" s="39">
-        <v>46255.490277777775</v>
+        <v>46255.695833333331</v>
       </c>
       <c r="J50" s="40" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="K50" s="36"/>
       <c r="L50" s="40"/>
       <c r="M50" s="41"/>
       <c r="N50" s="25"/>
       <c r="O50" s="34"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="12"/>
-      <c r="R50" s="12"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
     </row>
     <row r="51" spans="1:18" ht="19.5" customHeight="1">
       <c r="A51" s="36">
@@ -4106,13 +3908,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="37">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="E51" s="38" t="s">
         <v>80</v>
@@ -4124,13 +3926,13 @@
         <v>26</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I51" s="39">
-        <v>46255.582638888889</v>
+        <v>46255.714583333334</v>
       </c>
       <c r="J51" s="40" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K51" s="36"/>
       <c r="L51" s="40"/>
@@ -4141,46 +3943,46 @@
       <c r="Q51" s="12"/>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="1:18" ht="87.95" customHeight="1">
+    <row r="52" spans="1:18" ht="19.5" customHeight="1">
       <c r="A52" s="36">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="B52" s="37">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="F52" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G52" s="36" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="H52" s="38" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="I52" s="39">
-        <v>46255.695833333331</v>
+        <v>46257.555555555555</v>
       </c>
       <c r="J52" s="40" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="K52" s="36"/>
       <c r="L52" s="40"/>
       <c r="M52" s="41"/>
       <c r="N52" s="25"/>
       <c r="O52" s="34"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
+      <c r="P52" s="27"/>
+      <c r="Q52" s="12"/>
+      <c r="R52" s="12"/>
     </row>
     <row r="53" spans="1:18" ht="19.5" customHeight="1">
       <c r="A53" s="36">
@@ -4188,31 +3990,31 @@
         <v>52</v>
       </c>
       <c r="B53" s="37">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="F53" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G53" s="36" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="I53" s="39">
-        <v>46255.714583333334</v>
+        <v>46258.677777777775</v>
       </c>
       <c r="J53" s="40" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K53" s="36"/>
       <c r="L53" s="40"/>
@@ -4229,31 +4031,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C54" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="H54" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="I54" s="39">
+        <v>46258.772916666669</v>
+      </c>
+      <c r="J54" s="40" t="s">
         <v>178</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F54" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="H54" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="I54" s="39">
-        <v>46257.555555555555</v>
-      </c>
-      <c r="J54" s="40" t="s">
-        <v>179</v>
       </c>
       <c r="K54" s="36"/>
       <c r="L54" s="40"/>
@@ -4264,52 +4066,54 @@
       <c r="Q54" s="12"/>
       <c r="R54" s="12"/>
     </row>
-    <row r="55" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A55" s="46">
+    <row r="55" spans="1:18" s="14" customFormat="1" ht="87.95" customHeight="1">
+      <c r="A55" s="36">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="B55" s="47">
-        <v>62</v>
-      </c>
-      <c r="C55" s="48" t="s">
+      <c r="B55" s="37">
+        <v>65</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E55" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H55" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="I55" s="39">
+        <v>46258.822222222225</v>
+      </c>
+      <c r="J55" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="D55" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="E55" s="48" t="s">
+      <c r="K55" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="F55" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="G55" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H55" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="I55" s="49">
-        <v>46258.663888888885</v>
-      </c>
-      <c r="J55" s="50" t="s">
+      <c r="L55" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="K55" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="51"/>
-      <c r="N55" s="52"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q55" s="55" t="s">
+      <c r="M55" s="41"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="34"/>
+      <c r="P55" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q55" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="R55" s="55" t="s">
+      <c r="R55" s="17" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4319,31 +4123,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="37">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C56" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F56" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="I56" s="39">
+        <v>46258.848611111112</v>
+      </c>
+      <c r="J56" s="40" t="s">
         <v>185</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E56" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="I56" s="39">
-        <v>46258.677777777775</v>
-      </c>
-      <c r="J56" s="40" t="s">
-        <v>188</v>
       </c>
       <c r="K56" s="36"/>
       <c r="L56" s="40"/>
@@ -4360,13 +4164,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="37">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="E57" s="38" t="s">
         <v>30</v>
@@ -4375,16 +4179,16 @@
         <v>20</v>
       </c>
       <c r="G57" s="36" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="H57" s="38" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="I57" s="39">
-        <v>46258.772916666669</v>
+        <v>46259.470138888893</v>
       </c>
       <c r="J57" s="40" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="K57" s="36"/>
       <c r="L57" s="40"/>
@@ -4395,22 +4199,22 @@
       <c r="Q57" s="12"/>
       <c r="R57" s="12"/>
     </row>
-    <row r="58" spans="1:18" s="14" customFormat="1" ht="87.95" customHeight="1">
+    <row r="58" spans="1:18" ht="87.95" customHeight="1">
       <c r="A58" s="36">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
       <c r="B58" s="37">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>30</v>
+        <v>189</v>
       </c>
       <c r="F58" s="36" t="s">
         <v>20</v>
@@ -4419,31 +4223,27 @@
         <v>65</v>
       </c>
       <c r="H58" s="38" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="I58" s="39">
-        <v>46258.822222222225</v>
-      </c>
-      <c r="J58" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="K58" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="L58" s="40" t="s">
-        <v>196</v>
-      </c>
+        <v>46259.620138888888</v>
+      </c>
+      <c r="J58" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="K58" s="36"/>
+      <c r="L58" s="40"/>
       <c r="M58" s="41"/>
       <c r="N58" s="25"/>
       <c r="O58" s="34"/>
-      <c r="P58" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q58" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="R58" s="17" t="s">
-        <v>198</v>
+      <c r="P58" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q58" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="R58" s="18" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="19.5" customHeight="1">
@@ -4452,31 +4252,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="37">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C59" s="38" t="s">
         <v>193</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="F59" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G59" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I59" s="39">
-        <v>46258.848611111112</v>
+        <v>46259.634722222225</v>
       </c>
       <c r="J59" s="40" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K59" s="36"/>
       <c r="L59" s="40"/>
@@ -4493,16 +4293,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="37">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="F60" s="36" t="s">
         <v>20</v>
@@ -4511,13 +4311,13 @@
         <v>65</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="I60" s="39">
-        <v>46259.470138888893</v>
+        <v>46259.658333333333</v>
       </c>
       <c r="J60" s="40" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K60" s="36"/>
       <c r="L60" s="40"/>
@@ -4528,84 +4328,78 @@
       <c r="Q60" s="12"/>
       <c r="R60" s="12"/>
     </row>
-    <row r="61" spans="1:18" ht="87.95" customHeight="1">
+    <row r="61" spans="1:18" ht="19.5" customHeight="1">
       <c r="A61" s="36">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="B61" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="F61" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G61" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>186</v>
+        <v>59</v>
       </c>
       <c r="I61" s="39">
-        <v>46259.620138888888</v>
+        <v>46259.658333333333</v>
       </c>
       <c r="J61" s="40" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K61" s="36"/>
       <c r="L61" s="40"/>
       <c r="M61" s="41"/>
       <c r="N61" s="25"/>
       <c r="O61" s="34"/>
-      <c r="P61" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q61" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="R61" s="18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="19.5" customHeight="1">
+      <c r="P61" s="27"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+    </row>
+    <row r="62" spans="1:18" ht="63.95" customHeight="1">
       <c r="A62" s="36">
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
       <c r="B62" s="37">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>207</v>
+        <v>28</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E62" s="38" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F62" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G62" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H62" s="38" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="I62" s="39">
-        <v>46259.634722222225</v>
+        <v>46259.662499999999</v>
       </c>
       <c r="J62" s="40" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K62" s="36"/>
       <c r="L62" s="40"/>
@@ -4622,16 +4416,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="37">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="E63" s="38" t="s">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="F63" s="36" t="s">
         <v>20</v>
@@ -4640,13 +4434,13 @@
         <v>65</v>
       </c>
       <c r="H63" s="38" t="s">
-        <v>186</v>
+        <v>51</v>
       </c>
       <c r="I63" s="39">
-        <v>46259.658333333333</v>
+        <v>46259.744444444441</v>
       </c>
       <c r="J63" s="40" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K63" s="36"/>
       <c r="L63" s="40"/>
@@ -4663,31 +4457,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>171</v>
+        <v>92</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="F64" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G64" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H64" s="38" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I64" s="39">
-        <v>46259.658333333333</v>
+        <v>46260.391666666663</v>
       </c>
       <c r="J64" s="40" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="K64" s="36"/>
       <c r="L64" s="40"/>
@@ -4698,37 +4492,37 @@
       <c r="Q64" s="12"/>
       <c r="R64" s="12"/>
     </row>
-    <row r="65" spans="1:18" ht="63.95" customHeight="1">
+    <row r="65" spans="1:18" ht="19.5" customHeight="1">
       <c r="A65" s="36">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
       <c r="B65" s="37">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F65" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G65" s="36" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I65" s="39">
-        <v>46259.662499999999</v>
+        <v>46260.397916666669</v>
       </c>
       <c r="J65" s="40" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="K65" s="36"/>
       <c r="L65" s="40"/>
@@ -4745,31 +4539,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="37">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>90</v>
+        <v>206</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="F66" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G66" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H66" s="38" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I66" s="39">
-        <v>46259.744444444441</v>
+        <v>46260.433333333334</v>
       </c>
       <c r="J66" s="40" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K66" s="36"/>
       <c r="L66" s="40"/>
@@ -4786,31 +4580,31 @@
         <v>66</v>
       </c>
       <c r="B67" s="37">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="F67" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G67" s="36" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="H67" s="38" t="s">
         <v>51</v>
       </c>
       <c r="I67" s="39">
-        <v>46260.391666666663</v>
+        <v>46260.448611111111</v>
       </c>
       <c r="J67" s="40" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K67" s="36"/>
       <c r="L67" s="40"/>
@@ -4827,31 +4621,31 @@
         <v>67</v>
       </c>
       <c r="B68" s="37">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>71</v>
+        <v>210</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>36</v>
+        <v>211</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="F68" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G68" s="36" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="H68" s="38" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="I68" s="39">
-        <v>46260.397916666669</v>
+        <v>46260.566666666666</v>
       </c>
       <c r="J68" s="40" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K68" s="36"/>
       <c r="L68" s="40"/>
@@ -4868,31 +4662,31 @@
         <v>68</v>
       </c>
       <c r="B69" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="F69" s="36" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G69" s="36" t="s">
         <v>32</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I69" s="39">
-        <v>46260.433333333334</v>
+        <v>46260.570833333331</v>
       </c>
       <c r="J69" s="40" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="K69" s="36"/>
       <c r="L69" s="40"/>
@@ -4903,46 +4697,52 @@
       <c r="Q69" s="12"/>
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="1:18" ht="19.5" customHeight="1">
+    <row r="70" spans="1:18" ht="87.95" customHeight="1">
       <c r="A70" s="36">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="B70" s="37">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="F70" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G70" s="36" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="H70" s="38" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I70" s="39">
-        <v>46260.448611111111</v>
+        <v>46260.581250000003</v>
       </c>
       <c r="J70" s="40" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K70" s="36"/>
       <c r="L70" s="40"/>
       <c r="M70" s="41"/>
       <c r="N70" s="25"/>
       <c r="O70" s="34"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="12"/>
+      <c r="P70" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q70" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="R70" s="18" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="71" spans="1:18" ht="19.5" customHeight="1">
       <c r="A71" s="36">
@@ -4950,31 +4750,31 @@
         <v>70</v>
       </c>
       <c r="B71" s="37">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="F71" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G71" s="36" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="H71" s="38" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="I71" s="39">
-        <v>46260.566666666666</v>
+        <v>46260.736111111109</v>
       </c>
       <c r="J71" s="40" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K71" s="36"/>
       <c r="L71" s="40"/>
@@ -4991,31 +4791,31 @@
         <v>71</v>
       </c>
       <c r="B72" s="37">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>227</v>
+        <v>35</v>
       </c>
       <c r="D72" s="38" t="s">
         <v>36</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="F72" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G72" s="36" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H72" s="38" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="39">
-        <v>46260.570833333331</v>
+        <v>46260.747916666667</v>
       </c>
       <c r="J72" s="40" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="K72" s="36"/>
       <c r="L72" s="40"/>
@@ -5026,22 +4826,22 @@
       <c r="Q72" s="12"/>
       <c r="R72" s="12"/>
     </row>
-    <row r="73" spans="1:18" ht="87.95" customHeight="1">
+    <row r="73" spans="1:18" s="14" customFormat="1" ht="111.95" customHeight="1">
       <c r="A73" s="36">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="B73" s="37">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="F73" s="36" t="s">
         <v>20</v>
@@ -5050,69 +4850,79 @@
         <v>65</v>
       </c>
       <c r="H73" s="38" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="I73" s="39">
-        <v>46260.581250000003</v>
-      </c>
-      <c r="J73" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="K73" s="36"/>
-      <c r="L73" s="40"/>
+        <v>46260.805555555555</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="K73" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="L73" s="40" t="s">
+        <v>226</v>
+      </c>
       <c r="M73" s="41"/>
       <c r="N73" s="25"/>
       <c r="O73" s="34"/>
-      <c r="P73" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q73" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="R73" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="19.5" customHeight="1">
+      <c r="P73" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q73" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="R73" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="111.95" customHeight="1">
       <c r="A74" s="36">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="B74" s="37">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E74" s="38" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="F74" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G74" s="36" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H74" s="38" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I74" s="39">
-        <v>46260.736111111109</v>
+        <v>46261.277777777781</v>
       </c>
       <c r="J74" s="40" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="K74" s="36"/>
       <c r="L74" s="40"/>
       <c r="M74" s="41"/>
       <c r="N74" s="25"/>
       <c r="O74" s="34"/>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="12"/>
-      <c r="R74" s="12"/>
+      <c r="P74" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q74" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="R74" s="18" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="75" spans="1:18" ht="19.5" customHeight="1">
       <c r="A75" s="36">
@@ -5120,31 +4930,31 @@
         <v>74</v>
       </c>
       <c r="B75" s="37">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="E75" s="38" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="F75" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="36" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="I75" s="39">
-        <v>46260.747916666667</v>
+        <v>46261.4</v>
       </c>
       <c r="J75" s="40" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K75" s="36"/>
       <c r="L75" s="40"/>
@@ -5155,135 +4965,119 @@
       <c r="Q75" s="12"/>
       <c r="R75" s="12"/>
     </row>
-    <row r="76" spans="1:18" s="14" customFormat="1" ht="111.95" customHeight="1">
+    <row r="76" spans="1:18" ht="19.5" customHeight="1">
       <c r="A76" s="36">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B76" s="37">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="F76" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G76" s="36" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H76" s="38" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="I76" s="39">
-        <v>46260.805555555555</v>
-      </c>
-      <c r="J76" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="K76" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="L76" s="40" t="s">
-        <v>240</v>
-      </c>
+        <v>46261.483333333337</v>
+      </c>
+      <c r="J76" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="K76" s="36"/>
+      <c r="L76" s="40"/>
       <c r="M76" s="41"/>
       <c r="N76" s="25"/>
       <c r="O76" s="34"/>
-      <c r="P76" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q76" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="R76" s="17" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="111.95" customHeight="1">
+      <c r="P76" s="27"/>
+      <c r="Q76" s="12"/>
+      <c r="R76" s="12"/>
+    </row>
+    <row r="77" spans="1:18" ht="19.5" customHeight="1">
       <c r="A77" s="36">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="B77" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E77" s="38" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F77" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G77" s="36" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H77" s="38" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I77" s="39">
-        <v>46261.277777777781</v>
+        <v>46261.552777777775</v>
       </c>
       <c r="J77" s="40" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K77" s="36"/>
       <c r="L77" s="40"/>
       <c r="M77" s="41"/>
       <c r="N77" s="25"/>
       <c r="O77" s="34"/>
-      <c r="P77" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q77" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="R77" s="18" t="s">
-        <v>246</v>
-      </c>
+      <c r="P77" s="27"/>
+      <c r="Q77" s="12"/>
+      <c r="R77" s="12"/>
     </row>
     <row r="78" spans="1:18" ht="19.5" customHeight="1">
       <c r="A78" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A78:A108" si="3">ROW()-1</f>
         <v>77</v>
       </c>
       <c r="B78" s="37">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E78" s="38" t="s">
-        <v>108</v>
+        <v>240</v>
       </c>
       <c r="F78" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G78" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H78" s="38" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="I78" s="39">
-        <v>46261.4</v>
+        <v>46261.606944444444</v>
       </c>
       <c r="J78" s="40" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="K78" s="36"/>
       <c r="L78" s="40"/>
@@ -5294,88 +5088,78 @@
       <c r="Q78" s="12"/>
       <c r="R78" s="12"/>
     </row>
-    <row r="79" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A79" s="46">
-        <f t="shared" si="2"/>
+    <row r="79" spans="1:18" s="14" customFormat="1" ht="87.95" customHeight="1">
+      <c r="A79" s="36">
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
-      <c r="B79" s="47">
-        <v>87</v>
-      </c>
-      <c r="C79" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="D79" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="E79" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="F79" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="H79" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="I79" s="49">
-        <v>46261.427777777775</v>
-      </c>
-      <c r="J79" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="K79" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="L79" s="50" t="s">
-        <v>251</v>
-      </c>
-      <c r="M79" s="51"/>
-      <c r="N79" s="52"/>
-      <c r="O79" s="53"/>
-      <c r="P79" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q79" s="55" t="s">
-        <v>252</v>
-      </c>
-      <c r="R79" s="55" t="s">
-        <v>253</v>
-      </c>
+      <c r="B79" s="37">
+        <v>91</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D79" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F79" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H79" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="I79" s="39">
+        <v>46261.643055555556</v>
+      </c>
+      <c r="J79" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="K79" s="36"/>
+      <c r="L79" s="40"/>
+      <c r="M79" s="41"/>
+      <c r="N79" s="25"/>
+      <c r="O79" s="34"/>
+      <c r="P79" s="28"/>
+      <c r="Q79" s="16"/>
+      <c r="R79" s="16"/>
     </row>
     <row r="80" spans="1:18" ht="19.5" customHeight="1">
       <c r="A80" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>79</v>
       </c>
       <c r="B80" s="37">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E80" s="38" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="F80" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G80" s="36" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H80" s="38" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I80" s="39">
-        <v>46261.483333333337</v>
+        <v>46261.659722222219</v>
       </c>
       <c r="J80" s="40" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="K80" s="36"/>
       <c r="L80" s="40"/>
@@ -5388,35 +5172,35 @@
     </row>
     <row r="81" spans="1:18" ht="19.5" customHeight="1">
       <c r="A81" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="B81" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="E81" s="38" t="s">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="F81" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G81" s="36" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="H81" s="38" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="I81" s="39">
-        <v>46261.552777777775</v>
+        <v>46262.406944444447</v>
       </c>
       <c r="J81" s="40" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="K81" s="36"/>
       <c r="L81" s="40"/>
@@ -5429,35 +5213,35 @@
     </row>
     <row r="82" spans="1:18" ht="19.5" customHeight="1">
       <c r="A82" s="36">
-        <f t="shared" ref="A82:A113" si="3">ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="B82" s="37">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>258</v>
+        <v>108</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="F82" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G82" s="36" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H82" s="38" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="I82" s="39">
-        <v>46261.606944444444</v>
+        <v>46262.426388888889</v>
       </c>
       <c r="J82" s="40" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="K82" s="36"/>
       <c r="L82" s="40"/>
@@ -5468,46 +5252,46 @@
       <c r="Q82" s="12"/>
       <c r="R82" s="12"/>
     </row>
-    <row r="83" spans="1:18" s="14" customFormat="1" ht="87.95" customHeight="1">
+    <row r="83" spans="1:18" ht="19.5" customHeight="1">
       <c r="A83" s="36">
         <f t="shared" si="3"/>
         <v>82</v>
       </c>
       <c r="B83" s="37">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="E83" s="38" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="F83" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G83" s="36" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H83" s="38" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="I83" s="39">
-        <v>46261.643055555556</v>
+        <v>46262.426388888889</v>
       </c>
       <c r="J83" s="40" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="K83" s="36"/>
       <c r="L83" s="40"/>
       <c r="M83" s="41"/>
       <c r="N83" s="25"/>
       <c r="O83" s="34"/>
-      <c r="P83" s="28"/>
-      <c r="Q83" s="16"/>
-      <c r="R83" s="16"/>
+      <c r="P83" s="27"/>
+      <c r="Q83" s="12"/>
+      <c r="R83" s="12"/>
     </row>
     <row r="84" spans="1:18" ht="19.5" customHeight="1">
       <c r="A84" s="36">
@@ -5515,31 +5299,31 @@
         <v>83</v>
       </c>
       <c r="B84" s="37">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="F84" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G84" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H84" s="38" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="I84" s="39">
-        <v>46261.659722222219</v>
+        <v>46262.617361111115</v>
       </c>
       <c r="J84" s="40" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="K84" s="36"/>
       <c r="L84" s="40"/>
@@ -5556,16 +5340,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="37">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>115</v>
+        <v>250</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="E85" s="38" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F85" s="36" t="s">
         <v>20</v>
@@ -5574,13 +5358,13 @@
         <v>65</v>
       </c>
       <c r="H85" s="38" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I85" s="39">
-        <v>46262.406944444447</v>
+        <v>46262.670833333337</v>
       </c>
       <c r="J85" s="40" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="K85" s="36"/>
       <c r="L85" s="40"/>
@@ -5597,31 +5381,31 @@
         <v>85</v>
       </c>
       <c r="B86" s="37">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F86" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G86" s="36" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H86" s="38" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="I86" s="39">
-        <v>46262.426388888889</v>
+        <v>46262.720138888893</v>
       </c>
       <c r="J86" s="40" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="K86" s="36"/>
       <c r="L86" s="40"/>
@@ -5638,31 +5422,31 @@
         <v>86</v>
       </c>
       <c r="B87" s="37">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="E87" s="38" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F87" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G87" s="36" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="H87" s="38" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="I87" s="39">
-        <v>46262.426388888889</v>
+        <v>46262.792361111111</v>
       </c>
       <c r="J87" s="40" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="K87" s="36"/>
       <c r="L87" s="40"/>
@@ -5679,31 +5463,31 @@
         <v>87</v>
       </c>
       <c r="B88" s="37">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>115</v>
+        <v>257</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F88" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G88" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H88" s="38" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="I88" s="39">
-        <v>46262.617361111115</v>
+        <v>46265.409722222219</v>
       </c>
       <c r="J88" s="40" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K88" s="36"/>
       <c r="L88" s="40"/>
@@ -5720,31 +5504,31 @@
         <v>88</v>
       </c>
       <c r="B89" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>36</v>
+        <v>258</v>
       </c>
       <c r="E89" s="38" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F89" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G89" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H89" s="38" t="s">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="I89" s="39">
-        <v>46262.670833333337</v>
+        <v>46265.410416666666</v>
       </c>
       <c r="J89" s="40" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="K89" s="36"/>
       <c r="L89" s="40"/>
@@ -5761,31 +5545,31 @@
         <v>89</v>
       </c>
       <c r="B90" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="E90" s="38" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F90" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G90" s="36" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H90" s="38" t="s">
-        <v>18</v>
+        <v>259</v>
       </c>
       <c r="I90" s="39">
-        <v>46262.720138888893</v>
+        <v>46265.413888888885</v>
       </c>
       <c r="J90" s="40" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="K90" s="36"/>
       <c r="L90" s="40"/>
@@ -5802,31 +5586,31 @@
         <v>90</v>
       </c>
       <c r="B91" s="37">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D91" s="38" t="s">
-        <v>60</v>
+        <v>265</v>
       </c>
       <c r="E91" s="38" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="F91" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G91" s="36" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H91" s="38" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I91" s="39">
-        <v>46262.792361111111</v>
+        <v>46265.415972222225</v>
       </c>
       <c r="J91" s="40" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="K91" s="36"/>
       <c r="L91" s="40"/>
@@ -5837,73 +5621,63 @@
       <c r="Q91" s="12"/>
       <c r="R91" s="12"/>
     </row>
-    <row r="92" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A92" s="46">
+    <row r="92" spans="1:18" ht="19.5" customHeight="1">
+      <c r="A92" s="36">
         <f t="shared" si="3"/>
         <v>91</v>
       </c>
-      <c r="B92" s="47">
-        <v>100</v>
-      </c>
-      <c r="C92" s="48" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" s="48" t="s">
-        <v>276</v>
-      </c>
-      <c r="E92" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="F92" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H92" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="I92" s="49">
-        <v>46265.343055555553</v>
-      </c>
-      <c r="J92" s="57" t="s">
-        <v>277</v>
-      </c>
-      <c r="K92" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="L92" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="M92" s="51"/>
-      <c r="N92" s="52"/>
-      <c r="O92" s="53"/>
-      <c r="P92" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q92" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="R92" s="55" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" ht="19.5" customHeight="1">
+      <c r="B92" s="37">
+        <v>105</v>
+      </c>
+      <c r="C92" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="D92" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E92" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="F92" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H92" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="I92" s="39">
+        <v>46265.44027777778</v>
+      </c>
+      <c r="J92" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="K92" s="36"/>
+      <c r="L92" s="40"/>
+      <c r="M92" s="41"/>
+      <c r="N92" s="25"/>
+      <c r="O92" s="34"/>
+      <c r="P92" s="27"/>
+      <c r="Q92" s="12"/>
+      <c r="R92" s="12"/>
+    </row>
+    <row r="93" spans="1:18" ht="111.95" customHeight="1">
       <c r="A93" s="36">
         <f t="shared" si="3"/>
         <v>92</v>
       </c>
       <c r="B93" s="37">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D93" s="38" t="s">
-        <v>282</v>
+        <v>160</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F93" s="36" t="s">
         <v>20</v>
@@ -5912,22 +5686,22 @@
         <v>32</v>
       </c>
       <c r="H93" s="38" t="s">
-        <v>283</v>
+        <v>64</v>
       </c>
       <c r="I93" s="39">
-        <v>46265.409722222219</v>
+        <v>46265.454861111109</v>
       </c>
       <c r="J93" s="40" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="K93" s="36"/>
       <c r="L93" s="40"/>
       <c r="M93" s="41"/>
       <c r="N93" s="25"/>
       <c r="O93" s="34"/>
-      <c r="P93" s="27"/>
-      <c r="Q93" s="12"/>
-      <c r="R93" s="12"/>
+      <c r="P93" s="28"/>
+      <c r="Q93" s="16"/>
+      <c r="R93" s="16"/>
     </row>
     <row r="94" spans="1:18" ht="19.5" customHeight="1">
       <c r="A94" s="36">
@@ -5935,31 +5709,31 @@
         <v>93</v>
       </c>
       <c r="B94" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>282</v>
+        <v>160</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F94" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G94" s="36" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H94" s="38" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="I94" s="39">
-        <v>46265.410416666666</v>
+        <v>46265.463888888888</v>
       </c>
       <c r="J94" s="40" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="K94" s="36"/>
       <c r="L94" s="40"/>
@@ -5976,31 +5750,31 @@
         <v>94</v>
       </c>
       <c r="B95" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D95" s="38" t="s">
-        <v>282</v>
+        <v>18</v>
       </c>
       <c r="E95" s="38" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F95" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G95" s="36" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H95" s="38" t="s">
-        <v>283</v>
+        <v>18</v>
       </c>
       <c r="I95" s="39">
-        <v>46265.413888888885</v>
+        <v>46265.468055555553</v>
       </c>
       <c r="J95" s="40" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="K95" s="36"/>
       <c r="L95" s="40"/>
@@ -6017,31 +5791,31 @@
         <v>95</v>
       </c>
       <c r="B96" s="37">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>289</v>
+        <v>42</v>
       </c>
       <c r="E96" s="38" t="s">
-        <v>217</v>
+        <v>46</v>
       </c>
       <c r="F96" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G96" s="36" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H96" s="38" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="I96" s="39">
-        <v>46265.415972222225</v>
+        <v>46265.470833333333</v>
       </c>
       <c r="J96" s="40" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="K96" s="36"/>
       <c r="L96" s="40"/>
@@ -6052,87 +5826,93 @@
       <c r="Q96" s="12"/>
       <c r="R96" s="12"/>
     </row>
-    <row r="97" spans="1:18" ht="19.5" customHeight="1">
+    <row r="97" spans="1:18" ht="87.95" customHeight="1">
       <c r="A97" s="36">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="B97" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D97" s="38" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="E97" s="38" t="s">
-        <v>292</v>
+        <v>110</v>
       </c>
       <c r="F97" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G97" s="36" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H97" s="38" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="I97" s="39">
-        <v>46265.44027777778</v>
+        <v>46265.564583333333</v>
       </c>
       <c r="J97" s="40" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="K97" s="36"/>
       <c r="L97" s="40"/>
       <c r="M97" s="41"/>
       <c r="N97" s="25"/>
       <c r="O97" s="34"/>
-      <c r="P97" s="27"/>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="12"/>
-    </row>
-    <row r="98" spans="1:18" ht="111.95" customHeight="1">
+      <c r="P97" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q97" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="R97" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="19.5" customHeight="1">
       <c r="A98" s="36">
         <f t="shared" si="3"/>
         <v>97</v>
       </c>
       <c r="B98" s="37">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>171</v>
+        <v>284</v>
       </c>
       <c r="E98" s="38" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F98" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G98" s="36" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="H98" s="38" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="I98" s="39">
-        <v>46265.454861111109</v>
+        <v>46265.57430555555</v>
       </c>
       <c r="J98" s="40" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="K98" s="36"/>
       <c r="L98" s="40"/>
       <c r="M98" s="41"/>
       <c r="N98" s="25"/>
       <c r="O98" s="34"/>
-      <c r="P98" s="28"/>
-      <c r="Q98" s="16"/>
-      <c r="R98" s="16"/>
+      <c r="P98" s="27"/>
+      <c r="Q98" s="12"/>
+      <c r="R98" s="12"/>
     </row>
     <row r="99" spans="1:18" ht="19.5" customHeight="1">
       <c r="A99" s="36">
@@ -6140,31 +5920,31 @@
         <v>98</v>
       </c>
       <c r="B99" s="37">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D99" s="38" t="s">
-        <v>171</v>
+        <v>288</v>
       </c>
       <c r="E99" s="38" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F99" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G99" s="36" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="H99" s="38" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I99" s="39">
-        <v>46265.463888888888</v>
+        <v>46265.595138888893</v>
       </c>
       <c r="J99" s="40" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="K99" s="36"/>
       <c r="L99" s="40"/>
@@ -6181,13 +5961,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="37">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E100" s="38" t="s">
         <v>80</v>
@@ -6199,13 +5979,13 @@
         <v>26</v>
       </c>
       <c r="H100" s="38" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="I100" s="39">
-        <v>46265.468055555553</v>
+        <v>46265.59652777778</v>
       </c>
       <c r="J100" s="40" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="K100" s="36"/>
       <c r="L100" s="40"/>
@@ -6222,31 +6002,31 @@
         <v>100</v>
       </c>
       <c r="B101" s="37">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D101" s="38" t="s">
-        <v>42</v>
+        <v>293</v>
       </c>
       <c r="E101" s="38" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F101" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G101" s="36" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="H101" s="38" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I101" s="39">
-        <v>46265.470833333333</v>
+        <v>46265.59652777778</v>
       </c>
       <c r="J101" s="40" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="K101" s="36"/>
       <c r="L101" s="40"/>
@@ -6263,31 +6043,31 @@
         <v>101</v>
       </c>
       <c r="B102" s="37">
+        <v>115</v>
+      </c>
+      <c r="C102" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="D102" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E102" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C102" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E102" s="38" t="s">
-        <v>117</v>
-      </c>
       <c r="F102" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G102" s="36" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="H102" s="38" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I102" s="39">
-        <v>46265.564583333333</v>
+        <v>46265.597916666666</v>
       </c>
       <c r="J102" s="40" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="K102" s="36"/>
       <c r="L102" s="40"/>
@@ -6295,46 +6075,46 @@
       <c r="N102" s="25"/>
       <c r="O102" s="34"/>
       <c r="P102" s="30" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="Q102" s="18" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R102" s="18" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" ht="19.5" customHeight="1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="63.95" customHeight="1">
       <c r="A103" s="36">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
       <c r="B103" s="37">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D103" s="38" t="s">
-        <v>308</v>
+        <v>59</v>
       </c>
       <c r="E103" s="38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F103" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G103" s="36" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="H103" s="38" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I103" s="39">
-        <v>46265.57430555555</v>
+        <v>46265.598611111112</v>
       </c>
       <c r="J103" s="40" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="K103" s="36"/>
       <c r="L103" s="40"/>
@@ -6351,31 +6131,31 @@
         <v>103</v>
       </c>
       <c r="B104" s="37">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="D104" s="38" t="s">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="E104" s="38" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="F104" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G104" s="36" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="H104" s="38" t="s">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="I104" s="39">
-        <v>46265.595138888893</v>
+        <v>46265.599999999999</v>
       </c>
       <c r="J104" s="40" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="K104" s="36"/>
       <c r="L104" s="40"/>
@@ -6392,31 +6172,31 @@
         <v>104</v>
       </c>
       <c r="B105" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>314</v>
+        <v>287</v>
       </c>
       <c r="D105" s="38" t="s">
-        <v>59</v>
+        <v>288</v>
       </c>
       <c r="E105" s="38" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F105" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G105" s="36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H105" s="38" t="s">
-        <v>59</v>
+        <v>288</v>
       </c>
       <c r="I105" s="39">
-        <v>46265.59652777778</v>
+        <v>46265.599999999999</v>
       </c>
       <c r="J105" s="40" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="K105" s="36"/>
       <c r="L105" s="40"/>
@@ -6433,31 +6213,31 @@
         <v>105</v>
       </c>
       <c r="B106" s="37">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="D106" s="38" t="s">
-        <v>317</v>
+        <v>59</v>
       </c>
       <c r="E106" s="38" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F106" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G106" s="36" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H106" s="38" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I106" s="39">
-        <v>46265.59652777778</v>
+        <v>46265.604861111111</v>
       </c>
       <c r="J106" s="40" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="K106" s="36"/>
       <c r="L106" s="40"/>
@@ -6468,125 +6248,125 @@
       <c r="Q106" s="12"/>
       <c r="R106" s="12"/>
     </row>
-    <row r="107" spans="1:18" ht="87.95" customHeight="1">
+    <row r="107" spans="1:18" ht="19.5" customHeight="1">
       <c r="A107" s="36">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
       <c r="B107" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>319</v>
+        <v>136</v>
       </c>
       <c r="D107" s="38" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E107" s="38" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="F107" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G107" s="36" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="H107" s="38" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I107" s="39">
-        <v>46265.597916666666</v>
+        <v>46265.60555555555</v>
       </c>
       <c r="J107" s="40" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="K107" s="36"/>
       <c r="L107" s="40"/>
       <c r="M107" s="41"/>
       <c r="N107" s="25"/>
       <c r="O107" s="34"/>
-      <c r="P107" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q107" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="R107" s="18" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" ht="63.95" customHeight="1">
+      <c r="P107" s="27"/>
+      <c r="Q107" s="12"/>
+      <c r="R107" s="12"/>
+    </row>
+    <row r="108" spans="1:18" ht="111.95" customHeight="1">
       <c r="A108" s="36">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="B108" s="37">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D108" s="38" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E108" s="38" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F108" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G108" s="36" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="H108" s="38" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I108" s="39">
-        <v>46265.598611111112</v>
+        <v>46265.612500000003</v>
       </c>
       <c r="J108" s="40" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="K108" s="36"/>
       <c r="L108" s="40"/>
       <c r="M108" s="41"/>
       <c r="N108" s="25"/>
       <c r="O108" s="34"/>
-      <c r="P108" s="27"/>
-      <c r="Q108" s="12"/>
-      <c r="R108" s="12"/>
+      <c r="P108" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q108" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="R108" s="18" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="109" spans="1:18" ht="19.5" customHeight="1">
       <c r="A109" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A109:A125" si="4">ROW()-1</f>
         <v>108</v>
       </c>
       <c r="B109" s="37">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="E109" s="38" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F109" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G109" s="36" t="s">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="H109" s="38" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I109" s="39">
-        <v>46265.599999999999</v>
+        <v>46265.61319444445</v>
       </c>
       <c r="J109" s="40" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="K109" s="36"/>
       <c r="L109" s="40"/>
@@ -6599,17 +6379,17 @@
     </row>
     <row r="110" spans="1:18" ht="19.5" customHeight="1">
       <c r="A110" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>109</v>
       </c>
       <c r="B110" s="37">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>311</v>
+        <v>119</v>
       </c>
       <c r="D110" s="38" t="s">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="E110" s="38" t="s">
         <v>30</v>
@@ -6618,16 +6398,16 @@
         <v>20</v>
       </c>
       <c r="G110" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H110" s="38" t="s">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="I110" s="39">
-        <v>46265.599999999999</v>
+        <v>46265.622916666667</v>
       </c>
       <c r="J110" s="40" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="K110" s="36"/>
       <c r="L110" s="40"/>
@@ -6640,35 +6420,35 @@
     </row>
     <row r="111" spans="1:18" ht="19.5" customHeight="1">
       <c r="A111" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>110</v>
       </c>
       <c r="B111" s="37">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D111" s="38" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E111" s="38" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F111" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="H111" s="38" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I111" s="39">
-        <v>46265.604861111111</v>
+        <v>46265.630555555559</v>
       </c>
       <c r="J111" s="40" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K111" s="36"/>
       <c r="L111" s="40"/>
@@ -6681,35 +6461,35 @@
     </row>
     <row r="112" spans="1:18" ht="19.5" customHeight="1">
       <c r="A112" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>111</v>
       </c>
       <c r="B112" s="37">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>147</v>
+        <v>313</v>
       </c>
       <c r="D112" s="38" t="s">
-        <v>47</v>
+        <v>256</v>
       </c>
       <c r="E112" s="38" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F112" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G112" s="36" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H112" s="38" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="I112" s="39">
-        <v>46265.60555555555</v>
+        <v>46265.635416666672</v>
       </c>
       <c r="J112" s="40" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="K112" s="36"/>
       <c r="L112" s="40"/>
@@ -6720,19 +6500,19 @@
       <c r="Q112" s="12"/>
       <c r="R112" s="12"/>
     </row>
-    <row r="113" spans="1:18" ht="111.95" customHeight="1">
+    <row r="113" spans="1:18" ht="19.5" customHeight="1">
       <c r="A113" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="B113" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>328</v>
+        <v>90</v>
       </c>
       <c r="D113" s="38" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="E113" s="38" t="s">
         <v>30</v>
@@ -6741,45 +6521,39 @@
         <v>20</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="H113" s="38" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="I113" s="39">
-        <v>46265.612500000003</v>
+        <v>46265.665277777778</v>
       </c>
       <c r="J113" s="40" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="K113" s="36"/>
       <c r="L113" s="40"/>
       <c r="M113" s="41"/>
       <c r="N113" s="25"/>
       <c r="O113" s="34"/>
-      <c r="P113" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q113" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="R113" s="18" t="s">
-        <v>331</v>
-      </c>
+      <c r="P113" s="27"/>
+      <c r="Q113" s="12"/>
+      <c r="R113" s="12"/>
     </row>
     <row r="114" spans="1:18" ht="19.5" customHeight="1">
       <c r="A114" s="36">
-        <f t="shared" ref="A114:A133" si="4">ROW()-1</f>
+        <f t="shared" si="4"/>
         <v>113</v>
       </c>
       <c r="B114" s="37">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="D114" s="38" t="s">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="E114" s="38" t="s">
         <v>30</v>
@@ -6788,16 +6562,16 @@
         <v>20</v>
       </c>
       <c r="G114" s="36" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="H114" s="38" t="s">
-        <v>51</v>
+        <v>288</v>
       </c>
       <c r="I114" s="39">
-        <v>46265.61319444445</v>
+        <v>46265.66805555555</v>
       </c>
       <c r="J114" s="40" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="K114" s="36"/>
       <c r="L114" s="40"/>
@@ -6814,13 +6588,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="37">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>130</v>
+        <v>318</v>
       </c>
       <c r="D115" s="38" t="s">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="E115" s="38" t="s">
         <v>30</v>
@@ -6829,16 +6603,16 @@
         <v>20</v>
       </c>
       <c r="G115" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H115" s="38" t="s">
-        <v>59</v>
+        <v>319</v>
       </c>
       <c r="I115" s="39">
-        <v>46265.622916666667</v>
+        <v>46265.669444444444</v>
       </c>
       <c r="J115" s="40" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="K115" s="36"/>
       <c r="L115" s="40"/>
@@ -6855,31 +6629,31 @@
         <v>115</v>
       </c>
       <c r="B116" s="37">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D116" s="38" t="s">
-        <v>42</v>
+        <v>265</v>
       </c>
       <c r="E116" s="38" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F116" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G116" s="36" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="H116" s="38" t="s">
-        <v>42</v>
+        <v>319</v>
       </c>
       <c r="I116" s="39">
-        <v>46265.630555555559</v>
+        <v>46265.670833333337</v>
       </c>
       <c r="J116" s="40" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="K116" s="36"/>
       <c r="L116" s="40"/>
@@ -6896,16 +6670,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="37">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D117" s="38" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="E117" s="38" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F117" s="36" t="s">
         <v>20</v>
@@ -6914,13 +6688,13 @@
         <v>65</v>
       </c>
       <c r="H117" s="38" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I117" s="39">
-        <v>46265.635416666672</v>
+        <v>46265.681944444441</v>
       </c>
       <c r="J117" s="40" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="K117" s="36"/>
       <c r="L117" s="40"/>
@@ -6937,13 +6711,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="37">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>97</v>
+        <v>322</v>
       </c>
       <c r="D118" s="38" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="E118" s="38" t="s">
         <v>30</v>
@@ -6952,16 +6726,16 @@
         <v>20</v>
       </c>
       <c r="G118" s="36" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="H118" s="38" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="I118" s="39">
-        <v>46265.665277777778</v>
+        <v>46265.684027777781</v>
       </c>
       <c r="J118" s="40" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="K118" s="36"/>
       <c r="L118" s="40"/>
@@ -6978,13 +6752,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="37">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="D119" s="38" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="E119" s="38" t="s">
         <v>30</v>
@@ -6993,16 +6767,16 @@
         <v>20</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H119" s="38" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="I119" s="39">
-        <v>46265.66805555555</v>
+        <v>46265.688194444447</v>
       </c>
       <c r="J119" s="40" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="K119" s="36"/>
       <c r="L119" s="40"/>
@@ -7019,13 +6793,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="37">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="D120" s="38" t="s">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c r="E120" s="38" t="s">
         <v>30</v>
@@ -7034,16 +6808,16 @@
         <v>20</v>
       </c>
       <c r="G120" s="36" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="H120" s="38" t="s">
-        <v>343</v>
+        <v>24</v>
       </c>
       <c r="I120" s="39">
-        <v>46265.669444444444</v>
+        <v>46265.691666666666</v>
       </c>
       <c r="J120" s="40" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="K120" s="36"/>
       <c r="L120" s="40"/>
@@ -7054,54 +6828,46 @@
       <c r="Q120" s="12"/>
       <c r="R120" s="12"/>
     </row>
-    <row r="121" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A121" s="46">
+    <row r="121" spans="1:18" ht="19.5" customHeight="1">
+      <c r="A121" s="36">
         <f t="shared" si="4"/>
         <v>120</v>
       </c>
-      <c r="B121" s="47">
-        <v>131</v>
-      </c>
-      <c r="C121" s="48" t="s">
-        <v>345</v>
-      </c>
-      <c r="D121" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="E121" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G121" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="H121" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="I121" s="49">
-        <v>46265.677777777775</v>
-      </c>
-      <c r="J121" s="50" t="s">
-        <v>346</v>
-      </c>
-      <c r="K121" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="L121" s="50"/>
-      <c r="M121" s="51"/>
-      <c r="N121" s="52"/>
-      <c r="O121" s="53"/>
-      <c r="P121" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q121" s="55" t="s">
-        <v>347</v>
-      </c>
-      <c r="R121" s="55" t="s">
-        <v>348</v>
-      </c>
+      <c r="B121" s="37">
+        <v>136</v>
+      </c>
+      <c r="C121" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="D121" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="E121" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F121" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G121" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H121" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="I121" s="39">
+        <v>46265.694444444445</v>
+      </c>
+      <c r="J121" s="40" t="s">
+        <v>329</v>
+      </c>
+      <c r="K121" s="36"/>
+      <c r="L121" s="40"/>
+      <c r="M121" s="41"/>
+      <c r="N121" s="25"/>
+      <c r="O121" s="34"/>
+      <c r="P121" s="27"/>
+      <c r="Q121" s="12"/>
+      <c r="R121" s="12"/>
     </row>
     <row r="122" spans="1:18" ht="19.5" customHeight="1">
       <c r="A122" s="36">
@@ -7109,13 +6875,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="37">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D122" s="38" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="E122" s="38" t="s">
         <v>30</v>
@@ -7124,16 +6890,16 @@
         <v>20</v>
       </c>
       <c r="G122" s="36" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H122" s="38" t="s">
-        <v>343</v>
+        <v>92</v>
       </c>
       <c r="I122" s="39">
-        <v>46265.670833333337</v>
+        <v>46265.697916666672</v>
       </c>
       <c r="J122" s="40" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="K122" s="36"/>
       <c r="L122" s="40"/>
@@ -7144,56 +6910,46 @@
       <c r="Q122" s="12"/>
       <c r="R122" s="12"/>
     </row>
-    <row r="123" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A123" s="46">
+    <row r="123" spans="1:18" ht="19.5" customHeight="1">
+      <c r="A123" s="36">
         <f t="shared" si="4"/>
         <v>122</v>
       </c>
-      <c r="B123" s="47">
-        <v>129</v>
-      </c>
-      <c r="C123" s="48" t="s">
-        <v>335</v>
-      </c>
-      <c r="D123" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E123" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="F123" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G123" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="H123" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="I123" s="49">
-        <v>46265.670138888891</v>
-      </c>
-      <c r="J123" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="K123" s="46" t="s">
-        <v>400</v>
-      </c>
-      <c r="L123" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="M123" s="51"/>
-      <c r="N123" s="52"/>
-      <c r="O123" s="53"/>
-      <c r="P123" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q123" s="55" t="s">
-        <v>353</v>
-      </c>
-      <c r="R123" s="55" t="s">
-        <v>354</v>
-      </c>
+      <c r="B123" s="37">
+        <v>138</v>
+      </c>
+      <c r="C123" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="D123" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E123" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="F123" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H123" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="I123" s="39">
+        <v>46265.712500000001</v>
+      </c>
+      <c r="J123" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="K123" s="36"/>
+      <c r="L123" s="40"/>
+      <c r="M123" s="41"/>
+      <c r="N123" s="25"/>
+      <c r="O123" s="34"/>
+      <c r="P123" s="27"/>
+      <c r="Q123" s="12"/>
+      <c r="R123" s="12"/>
     </row>
     <row r="124" spans="1:18" ht="19.5" customHeight="1">
       <c r="A124" s="36">
@@ -7201,16 +6957,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="37">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="D124" s="38" t="s">
-        <v>356</v>
+        <v>33</v>
       </c>
       <c r="E124" s="38" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="F124" s="36" t="s">
         <v>20</v>
@@ -7219,13 +6975,13 @@
         <v>65</v>
       </c>
       <c r="H124" s="38" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="I124" s="39">
-        <v>46265.681944444441</v>
+        <v>46265.763888888891</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="K124" s="36"/>
       <c r="L124" s="40"/>
@@ -7242,31 +6998,31 @@
         <v>124</v>
       </c>
       <c r="B125" s="37">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C125" s="38" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="D125" s="38" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="E125" s="38" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="F125" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="H125" s="38" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="I125" s="39">
-        <v>46265.684027777781</v>
+        <v>46265.765972222223</v>
       </c>
       <c r="J125" s="40" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="K125" s="36"/>
       <c r="L125" s="40"/>
@@ -7277,78 +7033,84 @@
       <c r="Q125" s="12"/>
       <c r="R125" s="12"/>
     </row>
-    <row r="126" spans="1:18" ht="19.5" customHeight="1">
+    <row r="126" spans="1:18" ht="111.95" customHeight="1">
       <c r="A126" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A126:A135" si="5">ROW()-1</f>
         <v>125</v>
       </c>
       <c r="B126" s="37">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C126" s="38" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D126" s="38" t="s">
-        <v>308</v>
+        <v>54</v>
       </c>
       <c r="E126" s="38" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="F126" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G126" s="36" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="H126" s="38" t="s">
-        <v>308</v>
+        <v>59</v>
       </c>
       <c r="I126" s="39">
-        <v>46265.688194444447</v>
+        <v>46265.779861111107</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="K126" s="36"/>
       <c r="L126" s="40"/>
       <c r="M126" s="41"/>
       <c r="N126" s="25"/>
       <c r="O126" s="34"/>
-      <c r="P126" s="27"/>
-      <c r="Q126" s="12"/>
-      <c r="R126" s="12"/>
+      <c r="P126" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q126" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="R126" s="17" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="127" spans="1:18" ht="19.5" customHeight="1">
       <c r="A127" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>126</v>
       </c>
       <c r="B127" s="37">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C127" s="38" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D127" s="38" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="E127" s="38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F127" s="36" t="s">
         <v>20</v>
       </c>
       <c r="G127" s="36" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="H127" s="38" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="I127" s="39">
-        <v>46265.691666666666</v>
+        <v>46265.893750000003</v>
       </c>
       <c r="J127" s="40" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="K127" s="36"/>
       <c r="L127" s="40"/>
@@ -7361,35 +7123,35 @@
     </row>
     <row r="128" spans="1:18" ht="19.5" customHeight="1">
       <c r="A128" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>127</v>
       </c>
       <c r="B128" s="37">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C128" s="38" t="s">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="D128" s="38" t="s">
-        <v>282</v>
+        <v>91</v>
       </c>
       <c r="E128" s="38" t="s">
-        <v>30</v>
+        <v>203</v>
       </c>
       <c r="F128" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G128" s="36" t="s">
         <v>65</v>
       </c>
       <c r="H128" s="38" t="s">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="I128" s="39">
-        <v>46265.694444444445</v>
+        <v>46275.426388888889</v>
       </c>
       <c r="J128" s="40" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="K128" s="36"/>
       <c r="L128" s="40"/>
@@ -7402,35 +7164,35 @@
     </row>
     <row r="129" spans="1:18" ht="19.5" customHeight="1">
       <c r="A129" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>128</v>
       </c>
       <c r="B129" s="37">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C129" s="38" t="s">
-        <v>363</v>
+        <v>53</v>
       </c>
       <c r="D129" s="38" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="E129" s="38" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F129" s="36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G129" s="36" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="H129" s="38" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I129" s="39">
-        <v>46265.697916666672</v>
+        <v>46288.70694444445</v>
       </c>
       <c r="J129" s="40" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="K129" s="36"/>
       <c r="L129" s="40"/>
@@ -7441,617 +7203,268 @@
       <c r="Q129" s="12"/>
       <c r="R129" s="12"/>
     </row>
-    <row r="130" spans="1:18" ht="19.5" customHeight="1">
+    <row r="130" spans="1:18" s="9" customFormat="1" ht="19.5" customHeight="1">
       <c r="A130" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>129</v>
       </c>
       <c r="B130" s="37">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C130" s="38" t="s">
-        <v>365</v>
+        <v>202</v>
       </c>
       <c r="D130" s="38" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="E130" s="38" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F130" s="36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G130" s="36" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H130" s="38" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I130" s="39">
-        <v>46265.712500000001</v>
+        <v>46296.429166666669</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="K130" s="36"/>
       <c r="L130" s="40"/>
-      <c r="M130" s="41"/>
-      <c r="N130" s="25"/>
-      <c r="O130" s="34"/>
-      <c r="P130" s="27"/>
-      <c r="Q130" s="12"/>
-      <c r="R130" s="12"/>
-    </row>
-    <row r="131" spans="1:18" ht="19.5" customHeight="1">
+      <c r="M130" s="43"/>
+      <c r="N130" s="26"/>
+      <c r="O130" s="23"/>
+      <c r="P130" s="31"/>
+      <c r="Q130" s="13"/>
+      <c r="R130" s="13"/>
+    </row>
+    <row r="131" spans="1:18" s="9" customFormat="1" ht="87.95" customHeight="1">
       <c r="A131" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>130</v>
       </c>
-      <c r="B131" s="37">
-        <v>139</v>
-      </c>
-      <c r="C131" s="38" t="s">
-        <v>367</v>
-      </c>
-      <c r="D131" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E131" s="38" t="s">
-        <v>174</v>
+      <c r="B131" s="36">
+        <v>148</v>
+      </c>
+      <c r="C131" s="36" t="s">
+        <v>348</v>
+      </c>
+      <c r="D131" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E131" s="36" t="s">
+        <v>110</v>
       </c>
       <c r="F131" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G131" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="H131" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="I131" s="39">
-        <v>46265.763888888891</v>
-      </c>
-      <c r="J131" s="40" t="s">
-        <v>368</v>
+        <v>124</v>
+      </c>
+      <c r="H131" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="I131" s="44">
+        <v>46310.611111111109</v>
+      </c>
+      <c r="J131" s="45" t="s">
+        <v>349</v>
       </c>
       <c r="K131" s="36"/>
-      <c r="L131" s="40"/>
-      <c r="M131" s="41"/>
-      <c r="N131" s="25"/>
-      <c r="O131" s="34"/>
-      <c r="P131" s="27"/>
-      <c r="Q131" s="12"/>
-      <c r="R131" s="12"/>
-    </row>
-    <row r="132" spans="1:18" ht="19.5" customHeight="1">
+      <c r="L131" s="45"/>
+      <c r="M131" s="43"/>
+      <c r="N131" s="26"/>
+      <c r="O131" s="23"/>
+      <c r="P131" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q131" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="R131" s="19" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" s="15" customFormat="1" ht="87.95" customHeight="1">
       <c r="A132" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>131</v>
       </c>
-      <c r="B132" s="37">
-        <v>140</v>
-      </c>
-      <c r="C132" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="D132" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E132" s="38" t="s">
-        <v>174</v>
+      <c r="B132" s="36">
+        <v>150</v>
+      </c>
+      <c r="C132" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D132" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="E132" s="36" t="s">
+        <v>110</v>
       </c>
       <c r="F132" s="36" t="s">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="G132" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="H132" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="I132" s="39">
-        <v>46265.765972222223</v>
-      </c>
-      <c r="J132" s="40" t="s">
-        <v>370</v>
+        <v>32</v>
+      </c>
+      <c r="H132" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="I132" s="44">
+        <v>46314.628472222219</v>
+      </c>
+      <c r="J132" s="45" t="s">
+        <v>353</v>
       </c>
       <c r="K132" s="36"/>
-      <c r="L132" s="40"/>
-      <c r="M132" s="41"/>
-      <c r="N132" s="25"/>
-      <c r="O132" s="34"/>
-      <c r="P132" s="27"/>
-      <c r="Q132" s="12"/>
-      <c r="R132" s="12"/>
-    </row>
-    <row r="133" spans="1:18" s="56" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A133" s="46">
-        <f t="shared" si="4"/>
+      <c r="L132" s="45"/>
+      <c r="M132" s="43"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="23"/>
+      <c r="P132" s="28"/>
+      <c r="Q132" s="20"/>
+      <c r="R132" s="20"/>
+    </row>
+    <row r="133" spans="1:18" s="9" customFormat="1" ht="111.95" customHeight="1">
+      <c r="A133" s="36">
+        <f t="shared" si="5"/>
         <v>132</v>
       </c>
-      <c r="B133" s="47">
-        <v>141</v>
-      </c>
-      <c r="C133" s="48" t="s">
-        <v>371</v>
-      </c>
-      <c r="D133" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="E133" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="F133" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G133" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H133" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="I133" s="49">
-        <v>46265.774305555555</v>
-      </c>
-      <c r="J133" s="57" t="s">
-        <v>372</v>
-      </c>
-      <c r="K133" s="46" t="s">
-        <v>401</v>
-      </c>
-      <c r="L133" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="M133" s="51"/>
-      <c r="N133" s="52"/>
-      <c r="O133" s="53"/>
-      <c r="P133" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q133" s="55" t="s">
-        <v>374</v>
-      </c>
-      <c r="R133" s="55" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="134" spans="1:18" ht="111.95" customHeight="1">
+      <c r="B133" s="36">
+        <v>152</v>
+      </c>
+      <c r="C133" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D133" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E133" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="F133" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G133" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="I133" s="44">
+        <v>46316.39166666667</v>
+      </c>
+      <c r="J133" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="K133" s="36"/>
+      <c r="L133" s="45"/>
+      <c r="M133" s="43"/>
+      <c r="N133" s="26"/>
+      <c r="O133" s="23"/>
+      <c r="P133" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q133" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="R133" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" s="9" customFormat="1" ht="19.5" customHeight="1">
       <c r="A134" s="36">
-        <f t="shared" ref="A134:A143" si="5">ROW()-1</f>
+        <f t="shared" si="5"/>
         <v>133</v>
       </c>
-      <c r="B134" s="37">
-        <v>142</v>
-      </c>
-      <c r="C134" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="D134" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E134" s="38" t="s">
-        <v>210</v>
+      <c r="B134" s="36">
+        <v>153</v>
+      </c>
+      <c r="C134" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="D134" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E134" s="36" t="s">
+        <v>110</v>
       </c>
       <c r="F134" s="36" t="s">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="G134" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="H134" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I134" s="39">
-        <v>46265.779861111107</v>
-      </c>
-      <c r="J134" s="40" t="s">
-        <v>377</v>
+      <c r="I134" s="44">
+        <v>46316.447222222225</v>
+      </c>
+      <c r="J134" s="45" t="s">
+        <v>358</v>
       </c>
       <c r="K134" s="36"/>
-      <c r="L134" s="40"/>
-      <c r="M134" s="41"/>
-      <c r="N134" s="25"/>
-      <c r="O134" s="34"/>
-      <c r="P134" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q134" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="R134" s="17" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="135" spans="1:18" ht="19.5" customHeight="1">
+      <c r="L134" s="45"/>
+      <c r="M134" s="43"/>
+      <c r="N134" s="26"/>
+      <c r="O134" s="23"/>
+      <c r="P134" s="11"/>
+      <c r="Q134" s="11"/>
+      <c r="R134" s="11"/>
+    </row>
+    <row r="135" spans="1:18" s="9" customFormat="1" ht="19.5" customHeight="1">
       <c r="A135" s="36">
         <f t="shared" si="5"/>
         <v>134</v>
       </c>
-      <c r="B135" s="37">
-        <v>143</v>
-      </c>
-      <c r="C135" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="D135" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E135" s="38" t="s">
-        <v>25</v>
+      <c r="B135" s="36">
+        <v>154</v>
+      </c>
+      <c r="C135" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="D135" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="E135" s="36" t="s">
+        <v>101</v>
       </c>
       <c r="F135" s="36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G135" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H135" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="I135" s="39">
-        <v>46265.893750000003</v>
-      </c>
-      <c r="J135" s="40" t="s">
-        <v>381</v>
+      <c r="H135" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="I135" s="44">
+        <v>46317.484027777777</v>
+      </c>
+      <c r="J135" s="45" t="s">
+        <v>361</v>
       </c>
       <c r="K135" s="36"/>
-      <c r="L135" s="40"/>
-      <c r="M135" s="41"/>
-      <c r="N135" s="25"/>
-      <c r="O135" s="34"/>
-      <c r="P135" s="27"/>
-      <c r="Q135" s="12"/>
-      <c r="R135" s="12"/>
-    </row>
-    <row r="136" spans="1:18" ht="19.5" customHeight="1">
-      <c r="A136" s="36">
-        <f t="shared" si="5"/>
-        <v>135</v>
-      </c>
-      <c r="B136" s="37">
-        <v>144</v>
-      </c>
-      <c r="C136" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="D136" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="E136" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="F136" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G136" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="H136" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="I136" s="39">
-        <v>46275.426388888889</v>
-      </c>
-      <c r="J136" s="40" t="s">
-        <v>383</v>
-      </c>
-      <c r="K136" s="36"/>
-      <c r="L136" s="40"/>
-      <c r="M136" s="41"/>
-      <c r="N136" s="25"/>
-      <c r="O136" s="34"/>
-      <c r="P136" s="27"/>
-      <c r="Q136" s="12"/>
-      <c r="R136" s="12"/>
-    </row>
-    <row r="137" spans="1:18" ht="19.5" customHeight="1">
-      <c r="A137" s="36">
-        <f t="shared" si="5"/>
-        <v>136</v>
-      </c>
-      <c r="B137" s="37">
-        <v>146</v>
-      </c>
-      <c r="C137" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="D137" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E137" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F137" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="G137" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="H137" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="I137" s="39">
-        <v>46288.70694444445</v>
-      </c>
-      <c r="J137" s="40" t="s">
-        <v>384</v>
-      </c>
-      <c r="K137" s="36"/>
-      <c r="L137" s="40"/>
-      <c r="M137" s="41"/>
-      <c r="N137" s="25"/>
-      <c r="O137" s="34"/>
-      <c r="P137" s="27"/>
-      <c r="Q137" s="12"/>
-      <c r="R137" s="12"/>
-    </row>
-    <row r="138" spans="1:18" s="9" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A138" s="36">
-        <f t="shared" si="5"/>
-        <v>137</v>
-      </c>
-      <c r="B138" s="37">
-        <v>147</v>
-      </c>
-      <c r="C138" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D138" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="E138" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="F138" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="G138" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="H138" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I138" s="39">
-        <v>46296.429166666669</v>
-      </c>
-      <c r="J138" s="40" t="s">
-        <v>385</v>
-      </c>
-      <c r="K138" s="36"/>
-      <c r="L138" s="40"/>
-      <c r="M138" s="43"/>
-      <c r="N138" s="26"/>
-      <c r="O138" s="23"/>
-      <c r="P138" s="31"/>
-      <c r="Q138" s="13"/>
-      <c r="R138" s="13"/>
-    </row>
-    <row r="139" spans="1:18" s="9" customFormat="1" ht="87.95" customHeight="1">
-      <c r="A139" s="36">
-        <f t="shared" si="5"/>
-        <v>138</v>
-      </c>
-      <c r="B139" s="36">
-        <v>148</v>
-      </c>
-      <c r="C139" s="36" t="s">
-        <v>386</v>
-      </c>
-      <c r="D139" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E139" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="F139" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G139" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="H139" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="I139" s="44">
-        <v>46310.611111111109</v>
-      </c>
-      <c r="J139" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="K139" s="36"/>
-      <c r="L139" s="45"/>
-      <c r="M139" s="43"/>
-      <c r="N139" s="26"/>
-      <c r="O139" s="23"/>
-      <c r="P139" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q139" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="R139" s="19" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" s="15" customFormat="1" ht="87.95" customHeight="1">
-      <c r="A140" s="36">
-        <f t="shared" si="5"/>
-        <v>139</v>
-      </c>
-      <c r="B140" s="36">
-        <v>150</v>
-      </c>
-      <c r="C140" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D140" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="E140" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="F140" s="36" t="s">
-        <v>390</v>
-      </c>
-      <c r="G140" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="H140" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="I140" s="44">
-        <v>46314.628472222219</v>
-      </c>
-      <c r="J140" s="45" t="s">
-        <v>391</v>
-      </c>
-      <c r="K140" s="36"/>
-      <c r="L140" s="45"/>
-      <c r="M140" s="43"/>
-      <c r="N140" s="26"/>
-      <c r="O140" s="23"/>
-      <c r="P140" s="28"/>
-      <c r="Q140" s="20"/>
-      <c r="R140" s="20"/>
-    </row>
-    <row r="141" spans="1:18" s="9" customFormat="1" ht="111.95" customHeight="1">
-      <c r="A141" s="36">
-        <f t="shared" si="5"/>
-        <v>140</v>
-      </c>
-      <c r="B141" s="36">
-        <v>152</v>
-      </c>
-      <c r="C141" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D141" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="E141" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="F141" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G141" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="H141" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="I141" s="44">
-        <v>46316.39166666667</v>
-      </c>
-      <c r="J141" s="45" t="s">
-        <v>392</v>
-      </c>
-      <c r="K141" s="36"/>
-      <c r="L141" s="45"/>
-      <c r="M141" s="43"/>
-      <c r="N141" s="26"/>
-      <c r="O141" s="23"/>
-      <c r="P141" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q141" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="R141" s="21" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="142" spans="1:18" s="9" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A142" s="36">
-        <f t="shared" si="5"/>
-        <v>141</v>
-      </c>
-      <c r="B142" s="36">
-        <v>153</v>
-      </c>
-      <c r="C142" s="36" t="s">
-        <v>319</v>
-      </c>
-      <c r="D142" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="E142" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="F142" s="36" t="s">
-        <v>395</v>
-      </c>
-      <c r="G142" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="H142" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="I142" s="44">
-        <v>46316.447222222225</v>
-      </c>
-      <c r="J142" s="45" t="s">
-        <v>396</v>
-      </c>
-      <c r="K142" s="36"/>
-      <c r="L142" s="45"/>
-      <c r="M142" s="43"/>
-      <c r="N142" s="26"/>
-      <c r="O142" s="23"/>
-      <c r="P142" s="11"/>
-      <c r="Q142" s="11"/>
-      <c r="R142" s="11"/>
-    </row>
-    <row r="143" spans="1:18" s="9" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A143" s="36">
-        <f t="shared" si="5"/>
-        <v>142</v>
-      </c>
-      <c r="B143" s="36">
-        <v>154</v>
-      </c>
-      <c r="C143" s="36" t="s">
-        <v>397</v>
-      </c>
-      <c r="D143" s="36" t="s">
-        <v>398</v>
-      </c>
-      <c r="E143" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="F143" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="G143" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="H143" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="I143" s="44">
-        <v>46317.484027777777</v>
-      </c>
-      <c r="J143" s="45" t="s">
-        <v>399</v>
-      </c>
-      <c r="K143" s="36"/>
-      <c r="L143" s="45"/>
-      <c r="M143" s="43"/>
-      <c r="N143" s="26"/>
-      <c r="O143" s="23"/>
-      <c r="P143" s="11"/>
-      <c r="Q143" s="11"/>
-      <c r="R143" s="11"/>
+      <c r="L135" s="45"/>
+      <c r="M135" s="43"/>
+      <c r="N135" s="26"/>
+      <c r="O135" s="23"/>
+      <c r="P135" s="11"/>
+      <c r="Q135" s="11"/>
+      <c r="R135" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R143" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="10">
-      <filters blank="1">
-        <filter val="보류(채택결과 미확인)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R135"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>